--- a/data/sites/manufacturing/Production Operations/overall-equipment-effectiveness-oee-tracker.xlsx
+++ b/data/sites/manufacturing/Production Operations/overall-equipment-effectiveness-oee-tracker.xlsx
@@ -7,7 +7,18 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01 Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02 Architecture" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03 Controls" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04 KPIs" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05 RACI Matrix" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06 Procedures" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07 Risk Register" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08 Quality Audit" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09 Escalations" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10 SLAs" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11 Roadmap" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12 Sign-off" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +28,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,11 +38,15 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="14"/>
+      <color rgb="001F4E79"/>
+      <sz val="13"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -60,13 +75,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -141,6 +157,186 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4572000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4572000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4572000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4572000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4572000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4572000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -432,20 +628,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Overall Equipment Effectiveness (OEE) Tracker</t>
+          <t>Overall Equipment Effectiveness (OEE) Tracker - Section 1: Executive Summary &amp; Scope</t>
         </is>
       </c>
     </row>
@@ -456,127 +652,2567 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="45" customHeight="1">
+    <row r="3" ht="42" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Weekly OEE tracker broken down by availability, performance, and quality components for each production line.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+          <t>Weekly OEE tracker broken down by availability, performance, and quality components for each production line. Section 1 (Executive Summary &amp; Scope) applies to Production Operations within Manufacturing Knowledge Hub and is maintained by Grace Liu. Defines the operational charter, scope boundaries, and executive accountability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 1.1: Line 2 availability losses are driven primarily by changeover time. Secondary control 1.2: Performance component is calculated against the ideal cycle time, not the current standard.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Line</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Availability</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Quality</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>OEE</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Line 1</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>92%</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>88%</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>98%</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>79%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Line 2</t>
+          <t>Line 1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>81%</t>
+          <t>92%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>97%</t>
+          <t>98%</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>79%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>Line 2</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>81%</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>97%</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>71%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>Line 3</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>94%</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>91%</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>95%</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>81%</t>
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>• Line 2 availability losses are driven primarily by changeover time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>• Performance component is calculated against the ideal cycle time, not the current standard.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Section 1 review cadence is tracked by Grace Liu under Production Operations governance.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Overall Equipment Effectiveness (OEE) Tracker - Section 10: Cross-Functional Dependencies</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Manufacturing Knowledge Hub | Production Operations | Owner: Grace Liu  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Weekly OEE tracker broken down by availability, performance, and quality components for each production line. Section 10 (Cross-Functional Dependencies) applies to Production Operations within Manufacturing Knowledge Hub and is maintained by Grace Liu. Documents upstream and downstream team dependencies and service-level commitments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 10.1: Performance component is calculated against the ideal cycle time, not the current standard. Secondary control 10.2: Lines below 75% OEE trigger a root cause review with process engineering.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Availability</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>OEE</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Line 1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>92%</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>98%</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>79%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Line 2</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>81%</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>97%</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>71%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Line 3</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>94%</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>91%</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>81%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sec-10</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>92%</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>98%</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Stage 10 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>• Performance component is calculated against the ideal cycle time, not the current standard.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Lines below 75% OEE trigger a root cause review with process engineering.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Section 10 review cadence is tracked by Grace Liu under Production Operations governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Overall Equipment Effectiveness (OEE) Tracker - Section 11: Continuous Improvement Roadmap</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Manufacturing Knowledge Hub | Production Operations | Owner: Grace Liu  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Weekly OEE tracker broken down by availability, performance, and quality components for each production line. Section 11 (Continuous Improvement Roadmap) applies to Production Operations within Manufacturing Knowledge Hub and is maintained by Grace Liu. Schedules quarterly optimization milestones, automation targets, and capability reviews.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 11.1: Lines below 75% OEE trigger a root cause review with process engineering. Secondary control 11.2: OEE trends feed the monthly operations review deck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Availability</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>OEE</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Line 1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>92%</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>98%</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>79%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Line 2</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>81%</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>97%</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>71%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Line 3</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>94%</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>91%</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>81%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sec-11</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>81%</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>97%</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Stage 11 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>• Lines below 75% OEE trigger a root cause review with process engineering.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• OEE trends feed the monthly operations review deck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Section 11 review cadence is tracked by Grace Liu under Production Operations governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Overall Equipment Effectiveness (OEE) Tracker - Section 12: Appendix, Lineage &amp; Sign-off</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Manufacturing Knowledge Hub | Production Operations | Owner: Grace Liu  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Weekly OEE tracker broken down by availability, performance, and quality components for each production line. Section 12 (Appendix, Lineage &amp; Sign-off) applies to Production Operations within Manufacturing Knowledge Hub and is maintained by Grace Liu. Records document lineage, governance metadata, version history, and owner sign-off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 12.1: OEE trends feed the monthly operations review deck. Secondary control 12.2: Line 2 availability losses are driven primarily by changeover time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Availability</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>OEE</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Line 1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>92%</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>98%</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>79%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Line 2</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>81%</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>97%</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>71%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Line 3</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>94%</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>91%</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>81%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sec-12</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>94%</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>91%</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Stage 12 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>• OEE trends feed the monthly operations review deck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Line 2 availability losses are driven primarily by changeover time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Section 12 review cadence is tracked by Grace Liu under Production Operations governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Overall Equipment Effectiveness (OEE) Tracker - Section 2: Architecture &amp; Process Flow</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Manufacturing Knowledge Hub | Production Operations | Owner: Grace Liu  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Weekly OEE tracker broken down by availability, performance, and quality components for each production line. Section 2 (Architecture &amp; Process Flow) applies to Production Operations within Manufacturing Knowledge Hub and is maintained by Grace Liu. Maps end-to-end process stages, handoff gates, and system-of-record integrations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 2.1: Performance component is calculated against the ideal cycle time, not the current standard. Secondary control 2.2: Lines below 75% OEE trigger a root cause review with process engineering.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Availability</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>OEE</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Line 1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>92%</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>98%</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>79%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Line 2</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>81%</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>97%</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>71%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Line 3</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>94%</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>91%</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>81%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sec-2</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>81%</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>97%</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Stage 2 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>• Performance component is calculated against the ideal cycle time, not the current standard.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Lines below 75% OEE trigger a root cause review with process engineering.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Section 2 review cadence is tracked by Grace Liu under Production Operations governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Overall Equipment Effectiveness (OEE) Tracker - Section 3: Governance Standards &amp; Controls</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Manufacturing Knowledge Hub | Production Operations | Owner: Grace Liu  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Weekly OEE tracker broken down by availability, performance, and quality components for each production line. Section 3 (Governance Standards &amp; Controls) applies to Production Operations within Manufacturing Knowledge Hub and is maintained by Grace Liu. Establishes mandatory compliance controls, approval thresholds, and audit evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 3.1: Lines below 75% OEE trigger a root cause review with process engineering. Secondary control 3.2: OEE trends feed the monthly operations review deck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Availability</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>OEE</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Line 1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>92%</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>98%</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>79%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Line 2</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>81%</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>97%</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>71%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Line 3</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>94%</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>91%</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>81%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sec-3</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>94%</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>91%</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Stage 3 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>• Lines below 75% OEE trigger a root cause review with process engineering.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• OEE trends feed the monthly operations review deck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Section 3 review cadence is tracked by Grace Liu under Production Operations governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Overall Equipment Effectiveness (OEE) Tracker - Section 4: Operational KPIs &amp; Benchmarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Manufacturing Knowledge Hub | Production Operations | Owner: Grace Liu  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Weekly OEE tracker broken down by availability, performance, and quality components for each production line. Section 4 (Operational KPIs &amp; Benchmarks) applies to Production Operations within Manufacturing Knowledge Hub and is maintained by Grace Liu. Tracks baseline performance, target SLAs, and quarterly benchmark progression.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 4.1: OEE trends feed the monthly operations review deck. Secondary control 4.2: Line 2 availability losses are driven primarily by changeover time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Availability</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>OEE</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Line 1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>92%</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>98%</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>79%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Line 2</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>81%</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>97%</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>71%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Line 3</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>94%</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>91%</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>81%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sec-4</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>92%</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>98%</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Stage 4 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>• OEE trends feed the monthly operations review deck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Line 2 availability losses are driven primarily by changeover time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Section 4 review cadence is tracked by Grace Liu under Production Operations governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Overall Equipment Effectiveness (OEE) Tracker - Section 5: Roles, Responsibilities &amp; RACI</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Manufacturing Knowledge Hub | Production Operations | Owner: Grace Liu  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Weekly OEE tracker broken down by availability, performance, and quality components for each production line. Section 5 (Roles, Responsibilities &amp; RACI) applies to Production Operations within Manufacturing Knowledge Hub and is maintained by Grace Liu. Clarifies ownership across accountable executives, operational leads, and reviewers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 5.1: Line 2 availability losses are driven primarily by changeover time. Secondary control 5.2: Performance component is calculated against the ideal cycle time, not the current standard.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Availability</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>OEE</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Line 1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>92%</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>98%</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>79%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Line 2</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>81%</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>97%</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>71%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Line 3</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>94%</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>91%</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>81%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sec-5</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>81%</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>97%</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Stage 5 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>• Line 2 availability losses are driven primarily by changeover time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Performance component is calculated against the ideal cycle time, not the current standard.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Section 5 review cadence is tracked by Grace Liu under Production Operations governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Overall Equipment Effectiveness (OEE) Tracker - Section 6: Standard Operating Procedures</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Manufacturing Knowledge Hub | Production Operations | Owner: Grace Liu  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Weekly OEE tracker broken down by availability, performance, and quality components for each production line. Section 6 (Standard Operating Procedures) applies to Production Operations within Manufacturing Knowledge Hub and is maintained by Grace Liu. Provides step-by-step execution checklists, intake criteria, and verification gates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 6.1: Performance component is calculated against the ideal cycle time, not the current standard. Secondary control 6.2: Lines below 75% OEE trigger a root cause review with process engineering.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Availability</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>OEE</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Line 1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>92%</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>98%</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>79%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Line 2</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>81%</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>97%</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>71%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Line 3</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>94%</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>91%</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>81%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sec-6</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>94%</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>91%</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Stage 6 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>• Performance component is calculated against the ideal cycle time, not the current standard.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Lines below 75% OEE trigger a root cause review with process engineering.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Section 6 review cadence is tracked by Grace Liu under Production Operations governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Overall Equipment Effectiveness (OEE) Tracker - Section 7: Risk Register &amp; Mitigations</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Manufacturing Knowledge Hub | Production Operations | Owner: Grace Liu  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Weekly OEE tracker broken down by availability, performance, and quality components for each production line. Section 7 (Risk Register &amp; Mitigations) applies to Production Operations within Manufacturing Knowledge Hub and is maintained by Grace Liu. Catalogs operational, compliance, and delivery risks alongside preventive mitigations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 7.1: Lines below 75% OEE trigger a root cause review with process engineering. Secondary control 7.2: OEE trends feed the monthly operations review deck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Availability</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>OEE</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Line 1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>92%</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>98%</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>79%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Line 2</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>81%</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>97%</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>71%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Line 3</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>94%</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>91%</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>81%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sec-7</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>92%</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>98%</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Stage 7 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>• Lines below 75% OEE trigger a root cause review with process engineering.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• OEE trends feed the monthly operations review deck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Section 7 review cadence is tracked by Grace Liu under Production Operations governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Overall Equipment Effectiveness (OEE) Tracker - Section 8: Quality Assurance &amp; Audits</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Manufacturing Knowledge Hub | Production Operations | Owner: Grace Liu  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Weekly OEE tracker broken down by availability, performance, and quality components for each production line. Section 8 (Quality Assurance &amp; Audits) applies to Production Operations within Manufacturing Knowledge Hub and is maintained by Grace Liu. Specifies sampling frequencies, inspection tolerances, and nonconformance workflows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 8.1: OEE trends feed the monthly operations review deck. Secondary control 8.2: Line 2 availability losses are driven primarily by changeover time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Availability</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>OEE</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Line 1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>92%</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>98%</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>79%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Line 2</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>81%</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>97%</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>71%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Line 3</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>94%</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>91%</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>81%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sec-8</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>81%</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>97%</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Stage 8 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>• OEE trends feed the monthly operations review deck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Line 2 availability losses are driven primarily by changeover time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Section 8 review cadence is tracked by Grace Liu under Production Operations governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Overall Equipment Effectiveness (OEE) Tracker - Section 9: Exception Handling &amp; Escalations</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Manufacturing Knowledge Hub | Production Operations | Owner: Grace Liu  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Weekly OEE tracker broken down by availability, performance, and quality components for each production line. Section 9 (Exception Handling &amp; Escalations) applies to Production Operations within Manufacturing Knowledge Hub and is maintained by Grace Liu. Outlines severity tiers, response SLAs, and cross-functional escalation paths.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 9.1: Line 2 availability losses are driven primarily by changeover time. Secondary control 9.2: Performance component is calculated against the ideal cycle time, not the current standard.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Availability</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>OEE</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Line 1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>92%</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>98%</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>79%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Line 2</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>81%</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>97%</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>71%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Line 3</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>94%</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>91%</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>81%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sec-9</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>94%</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>91%</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Stage 9 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>• Line 2 availability losses are driven primarily by changeover time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Performance component is calculated against the ideal cycle time, not the current standard.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Section 9 review cadence is tracked by Grace Liu under Production Operations governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
 </file>
--- a/data/sites/manufacturing/Production Operations/overall-equipment-effectiveness-oee-tracker.xlsx
+++ b/data/sites/manufacturing/Production Operations/overall-equipment-effectiveness-oee-tracker.xlsx
@@ -15,10 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06 Procedures" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07 Risk Register" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08 Quality Audit" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09 Escalations" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10 SLAs" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11 Roadmap" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12 Sign-off" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09 Sign-off" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -280,36 +277,6 @@
 </file>
 
 <file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>16</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="4572000" cy="1524000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -813,661 +780,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Overall Equipment Effectiveness (OEE) Tracker - Section 10: Cross-Functional Dependencies</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Manufacturing Knowledge Hub | Production Operations | Owner: Grace Liu  |  Last updated: October 30, 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="42" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Weekly OEE tracker broken down by availability, performance, and quality components for each production line. Section 10 (Cross-Functional Dependencies) applies to Production Operations within Manufacturing Knowledge Hub and is maintained by Grace Liu. Documents upstream and downstream team dependencies and service-level commitments.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Operational requirement 10.1: Performance component is calculated against the ideal cycle time, not the current standard. Secondary control 10.2: Lines below 75% OEE trigger a root cause review with process engineering.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Line</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Availability</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Quality</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>OEE</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Line 1</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>92%</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>88%</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>98%</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>79%</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Line 2</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>81%</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>90%</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>97%</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>71%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Line 3</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>94%</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>91%</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>95%</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>81%</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Sec-10</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>92%</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>88%</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>98%</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Stage 10 Verified</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Governance Checkpoints</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>• Performance component is calculated against the ideal cycle time, not the current standard.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>• Lines below 75% OEE trigger a root cause review with process engineering.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>• Section 10 review cadence is tracked by Grace Liu under Production Operations governance.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A2:D2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Overall Equipment Effectiveness (OEE) Tracker - Section 11: Continuous Improvement Roadmap</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Manufacturing Knowledge Hub | Production Operations | Owner: Grace Liu  |  Last updated: October 30, 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="42" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Weekly OEE tracker broken down by availability, performance, and quality components for each production line. Section 11 (Continuous Improvement Roadmap) applies to Production Operations within Manufacturing Knowledge Hub and is maintained by Grace Liu. Schedules quarterly optimization milestones, automation targets, and capability reviews.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Operational requirement 11.1: Lines below 75% OEE trigger a root cause review with process engineering. Secondary control 11.2: OEE trends feed the monthly operations review deck.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Line</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Availability</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Quality</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>OEE</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Line 1</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>92%</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>88%</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>98%</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>79%</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Line 2</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>81%</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>90%</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>97%</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>71%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Line 3</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>94%</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>91%</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>95%</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>81%</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Sec-11</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>81%</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>90%</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>97%</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Stage 11 Verified</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Governance Checkpoints</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>• Lines below 75% OEE trigger a root cause review with process engineering.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>• OEE trends feed the monthly operations review deck.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>• Section 11 review cadence is tracked by Grace Liu under Production Operations governance.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A2:D2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Overall Equipment Effectiveness (OEE) Tracker - Section 12: Appendix, Lineage &amp; Sign-off</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Manufacturing Knowledge Hub | Production Operations | Owner: Grace Liu  |  Last updated: October 30, 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="42" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Weekly OEE tracker broken down by availability, performance, and quality components for each production line. Section 12 (Appendix, Lineage &amp; Sign-off) applies to Production Operations within Manufacturing Knowledge Hub and is maintained by Grace Liu. Records document lineage, governance metadata, version history, and owner sign-off.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Operational requirement 12.1: OEE trends feed the monthly operations review deck. Secondary control 12.2: Line 2 availability losses are driven primarily by changeover time.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Line</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Availability</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Quality</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>OEE</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Line 1</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>92%</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>88%</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>98%</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>79%</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Line 2</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>81%</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>90%</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>97%</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>71%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Line 3</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>94%</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>91%</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>95%</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>81%</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Sec-12</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>94%</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>91%</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>95%</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Stage 12 Verified</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Governance Checkpoints</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>• OEE trends feed the monthly operations review deck.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>• Line 2 availability losses are driven primarily by changeover time.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>• Section 12 review cadence is tracked by Grace Liu under Production Operations governance.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A2:D2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -3017,7 +2329,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Overall Equipment Effectiveness (OEE) Tracker - Section 9: Exception Handling &amp; Escalations</t>
+          <t>Overall Equipment Effectiveness (OEE) Tracker - Section 9: Appendix, Lineage &amp; Sign-off</t>
         </is>
       </c>
     </row>
@@ -3031,7 +2343,7 @@
     <row r="3" ht="42" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Weekly OEE tracker broken down by availability, performance, and quality components for each production line. Section 9 (Exception Handling &amp; Escalations) applies to Production Operations within Manufacturing Knowledge Hub and is maintained by Grace Liu. Outlines severity tiers, response SLAs, and cross-functional escalation paths.</t>
+          <t>Weekly OEE tracker broken down by availability, performance, and quality components for each production line. Section 9 (Appendix, Lineage &amp; Sign-off) applies to Production Operations within Manufacturing Knowledge Hub and is maintained by Grace Liu. Records document lineage, governance metadata, version history, and owner sign-off.</t>
         </is>
       </c>
     </row>
